--- a/src/evaluation/data/Backup/gpt_semantic_1500_300_400_10/run_1/ragas_results_20260116_192916.xlsx
+++ b/src/evaluation/data/Backup/gpt_semantic_1500_300_400_10/run_1/ragas_results_20260116_192916.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Köln\Masterarbeit\Software\uzk-masterarbeit\src\evaluation\data\Backup\gpt_semantic_1500_300_400_10\run_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCFF8B8-4ABD-4308-81C5-1C964450E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E467D978-5A4D-4DE2-8AC2-C4469FFF73EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detaillierte Ergebnisse" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Detaillierte Ergebnisse'!$A$1:$Z$117</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2419,7 +2432,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2522,7 +2534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2602,7 +2614,7 @@
         <v>27.344623327255249</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2636,6 +2648,9 @@
       <c r="K3">
         <v>0</v>
       </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
       <c r="M3">
         <v>0.55190290291312294</v>
       </c>
@@ -2679,7 +2694,7 @@
         <v>14.071793079376221</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2759,7 +2774,7 @@
         <v>11.182027816772459</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2839,7 +2854,7 @@
         <v>19.190554618835449</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2919,7 +2934,7 @@
         <v>14.060524463653559</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2999,7 +3014,7 @@
         <v>16.035509347915649</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3079,7 +3094,7 @@
         <v>15.58632922172546</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3159,7 +3174,7 @@
         <v>10.757596015930179</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3239,7 +3254,7 @@
         <v>18.807651519775391</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3319,7 +3334,7 @@
         <v>6.620689868927002</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3399,7 +3414,7 @@
         <v>9.8429596424102783</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3479,7 +3494,7 @@
         <v>8.5948774814605713</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3559,7 +3574,7 @@
         <v>8.9244847297668457</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3639,7 +3654,7 @@
         <v>9.9332442283630371</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3719,7 +3734,7 @@
         <v>12.71550178527832</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3799,7 +3814,7 @@
         <v>16.509256839752201</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3879,7 +3894,7 @@
         <v>11.32332706451416</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3959,7 +3974,7 @@
         <v>8.776602029800415</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4039,7 +4054,7 @@
         <v>9.2074813842773438</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4119,7 +4134,7 @@
         <v>12.139952421188349</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4199,7 +4214,7 @@
         <v>10.72093343734741</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="135" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4279,7 +4294,7 @@
         <v>10.7368278503418</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4359,7 +4374,7 @@
         <v>11.617148876190191</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4439,7 +4454,7 @@
         <v>8.093456506729126</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4519,7 +4534,7 @@
         <v>11.119332790374759</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4599,7 +4614,7 @@
         <v>14.6435112953186</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4679,7 +4694,7 @@
         <v>8.1190822124481201</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4759,7 +4774,7 @@
         <v>16.099664449691769</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4839,7 +4854,7 @@
         <v>13.47735691070557</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4919,7 +4934,7 @@
         <v>10.929827928543091</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4959,6 +4974,9 @@
       <c r="M32">
         <v>0.77979245052896318</v>
       </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
       <c r="O32">
         <v>0</v>
       </c>
@@ -4996,7 +5014,7 @@
         <v>11.53959274291992</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5033,6 +5051,9 @@
       <c r="L33">
         <v>0.91666666663611107</v>
       </c>
+      <c r="M33">
+        <v>0.77071931773562707</v>
+      </c>
       <c r="N33">
         <v>0.2499999996875</v>
       </c>
@@ -5073,7 +5094,7 @@
         <v>12.59057259559631</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5153,7 +5174,7 @@
         <v>8.6075434684753418</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5233,7 +5254,7 @@
         <v>22.423858642578121</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5313,7 +5334,7 @@
         <v>18.859132051467899</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5393,7 +5414,7 @@
         <v>13.552275419235229</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5473,7 +5494,7 @@
         <v>15.69378614425659</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5553,7 +5574,7 @@
         <v>10.47404503822327</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5633,7 +5654,7 @@
         <v>10.71195912361145</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5713,7 +5734,7 @@
         <v>10.67533707618713</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5793,7 +5814,7 @@
         <v>8.2464113235473633</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5873,7 +5894,7 @@
         <v>14.00822114944458</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5996,6 +6017,9 @@
       <c r="N45">
         <v>0.249999999375</v>
       </c>
+      <c r="O45">
+        <v>0.95648461052265299</v>
+      </c>
       <c r="P45">
         <v>0.33041563630104059</v>
       </c>
@@ -6030,7 +6054,7 @@
         <v>11.593264579772949</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6110,7 +6134,7 @@
         <v>12.42911648750305</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6190,7 +6214,7 @@
         <v>16.60448598861694</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6270,7 +6294,7 @@
         <v>11.682131767272949</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6350,7 +6374,7 @@
         <v>14.15609884262085</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6430,7 +6454,7 @@
         <v>10.841383695602421</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6510,7 +6534,7 @@
         <v>11.39180541038513</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6590,7 +6614,7 @@
         <v>9.8769991397857666</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6670,7 +6694,7 @@
         <v>8.3568201065063477</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6750,7 +6774,7 @@
         <v>12.13157224655151</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6830,7 +6854,7 @@
         <v>11.33696436882019</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6910,7 +6934,7 @@
         <v>13.220257520675659</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6987,7 +7011,7 @@
         <v>10.83357262611389</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -7107,6 +7131,9 @@
       <c r="N59">
         <v>0.49999999937499989</v>
       </c>
+      <c r="O59">
+        <v>0.94242794208617997</v>
+      </c>
       <c r="P59">
         <v>0.70373892784118652</v>
       </c>
@@ -7141,7 +7168,7 @@
         <v>9.4399549961090088</v>
       </c>
     </row>
-    <row r="60" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -7221,7 +7248,7 @@
         <v>17.07772779464722</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -7301,7 +7328,7 @@
         <v>9.5432624816894531</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7381,7 +7408,7 @@
         <v>18.39212274551392</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7461,7 +7488,7 @@
         <v>13.78679847717285</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7541,7 +7568,7 @@
         <v>9.2668333053588867</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7621,7 +7648,7 @@
         <v>8.3213164806365967</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7701,7 +7728,7 @@
         <v>13.107878923416139</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7781,7 +7808,7 @@
         <v>12.475814819335939</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7861,7 +7888,7 @@
         <v>13.542776107788089</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7941,7 +7968,7 @@
         <v>13.69088888168335</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -8021,7 +8048,7 @@
         <v>12.26931858062744</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -8101,7 +8128,7 @@
         <v>19.893660545349121</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -8181,7 +8208,7 @@
         <v>14.84006571769714</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -8261,7 +8288,7 @@
         <v>25.474005460739139</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -8341,7 +8368,7 @@
         <v>33.517132520675659</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -8421,7 +8448,7 @@
         <v>20.37201189994812</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -8461,6 +8488,9 @@
       <c r="M76">
         <v>0.61471803324663388</v>
       </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
       <c r="O76">
         <v>0</v>
       </c>
@@ -8498,7 +8528,7 @@
         <v>9.8003296852111816</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -8578,7 +8608,7 @@
         <v>9.3510410785675049</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -8658,7 +8688,7 @@
         <v>11.53910493850708</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -8738,7 +8768,7 @@
         <v>18.362339973449711</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -8818,7 +8848,7 @@
         <v>7.6907761096954346</v>
       </c>
     </row>
-    <row r="81" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -8898,7 +8928,7 @@
         <v>12.2669780254364</v>
       </c>
     </row>
-    <row r="82" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -8978,7 +9008,7 @@
         <v>11.566985845565799</v>
       </c>
     </row>
-    <row r="83" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9058,7 +9088,7 @@
         <v>12.899361610412599</v>
       </c>
     </row>
-    <row r="84" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9138,7 +9168,7 @@
         <v>9.9024527072906494</v>
       </c>
     </row>
-    <row r="85" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9218,7 +9248,7 @@
         <v>19.895704030990601</v>
       </c>
     </row>
-    <row r="86" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9298,7 +9328,7 @@
         <v>12.552891254425051</v>
       </c>
     </row>
-    <row r="87" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9378,7 +9408,7 @@
         <v>18.536498546600338</v>
       </c>
     </row>
-    <row r="88" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9458,7 +9488,7 @@
         <v>14.9645779132843</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9538,7 +9568,7 @@
         <v>16.10311579704285</v>
       </c>
     </row>
-    <row r="90" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9618,7 +9648,7 @@
         <v>9.9229226112365723</v>
       </c>
     </row>
-    <row r="91" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9698,7 +9728,7 @@
         <v>16.46701812744141</v>
       </c>
     </row>
-    <row r="92" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9778,7 +9808,7 @@
         <v>15.91425848007202</v>
       </c>
     </row>
-    <row r="93" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9858,7 +9888,7 @@
         <v>14.602725028991699</v>
       </c>
     </row>
-    <row r="94" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9938,7 +9968,7 @@
         <v>12.222115516662599</v>
       </c>
     </row>
-    <row r="95" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -10018,7 +10048,7 @@
         <v>10.13082122802734</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -10098,7 +10128,7 @@
         <v>18.247110605239872</v>
       </c>
     </row>
-    <row r="97" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -10178,7 +10208,7 @@
         <v>13.50137996673584</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -10258,7 +10288,7 @@
         <v>11.59838509559631</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -10338,7 +10368,7 @@
         <v>15.352930307388309</v>
       </c>
     </row>
-    <row r="100" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -10418,7 +10448,7 @@
         <v>15.8968780040741</v>
       </c>
     </row>
-    <row r="101" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -10498,7 +10528,7 @@
         <v>25.607762813568119</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10578,7 +10608,7 @@
         <v>15.07828521728516</v>
       </c>
     </row>
-    <row r="103" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10658,7 +10688,7 @@
         <v>11.60428619384766</v>
       </c>
     </row>
-    <row r="104" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10738,7 +10768,7 @@
         <v>8.0882086753845215</v>
       </c>
     </row>
-    <row r="105" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10818,7 +10848,7 @@
         <v>9.8486227989196777</v>
       </c>
     </row>
-    <row r="106" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10898,7 +10928,7 @@
         <v>12.61184287071228</v>
       </c>
     </row>
-    <row r="107" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10978,7 +11008,7 @@
         <v>12.432674884796141</v>
       </c>
     </row>
-    <row r="108" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -11058,7 +11088,7 @@
         <v>14.25144791603088</v>
       </c>
     </row>
-    <row r="109" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -11138,7 +11168,7 @@
         <v>15.517043352127081</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -11218,7 +11248,7 @@
         <v>12.85596370697021</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -11298,7 +11328,7 @@
         <v>16.17404580116272</v>
       </c>
     </row>
-    <row r="112" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -11378,7 +11408,7 @@
         <v>9.3000433444976807</v>
       </c>
     </row>
-    <row r="113" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -11458,7 +11488,7 @@
         <v>9.4279959201812744</v>
       </c>
     </row>
-    <row r="114" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -11538,7 +11568,7 @@
         <v>14.00123620033264</v>
       </c>
     </row>
-    <row r="115" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -11618,7 +11648,7 @@
         <v>9.237666130065918</v>
       </c>
     </row>
-    <row r="116" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -11698,7 +11728,7 @@
         <v>11.45024538040161</v>
       </c>
     </row>
-    <row r="117" spans="1:26" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -11779,11 +11809,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z117" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11842,7 +11867,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="4">
-        <v>0.58014132550850128</v>
+        <v>0.57509661833016634</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11850,7 +11875,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="5">
-        <v>0.77200388366020756</v>
+        <v>0.77199271352173338</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11858,7 +11883,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="4">
-        <v>0.25068398827134369</v>
+        <v>0.24636185054252757</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11866,7 +11891,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="5">
-        <v>0.63383611995639388</v>
+        <v>0.63927784678998045</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
